--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/31.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/31.xlsx
@@ -426,13 +426,13 @@
         <v>-21.12691049084888</v>
       </c>
       <c r="E2">
-        <v>-22.20130115604923</v>
+        <v>-20.36257897868716</v>
       </c>
       <c r="F2">
-        <v>-0.9168761219339322</v>
+        <v>-0.1506602969990706</v>
       </c>
       <c r="G2">
-        <v>-16.17712978026148</v>
+        <v>-17.42646766465906</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.27621118157749</v>
       </c>
       <c r="E3">
-        <v>-22.13920649353172</v>
+        <v>-20.92092424956314</v>
       </c>
       <c r="F3">
-        <v>-1.490958754728671</v>
+        <v>0.02344844882353785</v>
       </c>
       <c r="G3">
-        <v>-15.50162050326765</v>
+        <v>-17.00909706448385</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.08265315818129</v>
       </c>
       <c r="E4">
-        <v>-23.33094971713464</v>
+        <v>-20.83468281640307</v>
       </c>
       <c r="F4">
-        <v>-0.7875066711691222</v>
+        <v>0.06486516222870753</v>
       </c>
       <c r="G4">
-        <v>-15.52593567301698</v>
+        <v>-16.63185099792945</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.66847730522298</v>
       </c>
       <c r="E5">
-        <v>-23.90300058538255</v>
+        <v>-21.20371640867071</v>
       </c>
       <c r="F5">
-        <v>-1.654650780461075</v>
+        <v>0.02425196520425337</v>
       </c>
       <c r="G5">
-        <v>-15.41194534267979</v>
+        <v>-16.30034256586677</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.06513619838298</v>
       </c>
       <c r="E6">
-        <v>-23.87137388114398</v>
+        <v>-21.72860340911387</v>
       </c>
       <c r="F6">
-        <v>-1.041556184831494</v>
+        <v>-0.1476210169981992</v>
       </c>
       <c r="G6">
-        <v>-16.20606727330938</v>
+        <v>-16.19629786704943</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.358218342645</v>
       </c>
       <c r="E7">
-        <v>-23.18888912376888</v>
+        <v>-22.27551488921259</v>
       </c>
       <c r="F7">
-        <v>-1.492642825658562</v>
+        <v>0.0384443839164173</v>
       </c>
       <c r="G7">
-        <v>-15.50423255323105</v>
+        <v>-15.28181669465264</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.61694298541282</v>
       </c>
       <c r="E8">
-        <v>-24.63622097230176</v>
+        <v>-22.78233126718142</v>
       </c>
       <c r="F8">
-        <v>-1.17581548837503</v>
+        <v>-0.1030258578684879</v>
       </c>
       <c r="G8">
-        <v>-14.1444836693307</v>
+        <v>-15.36283854229324</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.90759964896929</v>
       </c>
       <c r="E9">
-        <v>-24.97515208888704</v>
+        <v>-23.44709427183347</v>
       </c>
       <c r="F9">
-        <v>-1.023497775450465</v>
+        <v>0.1889695097813239</v>
       </c>
       <c r="G9">
-        <v>-14.33698300563955</v>
+        <v>-14.35423872201452</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.293290801978515</v>
       </c>
       <c r="E10">
-        <v>-26.44292604356072</v>
+        <v>-23.43843067300988</v>
       </c>
       <c r="F10">
-        <v>-0.6190266818485363</v>
+        <v>0.4986422378068771</v>
       </c>
       <c r="G10">
-        <v>-13.75667061404378</v>
+        <v>-13.92404283903546</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.806491574435171</v>
       </c>
       <c r="E11">
-        <v>-26.68878784756792</v>
+        <v>-25.60283522283103</v>
       </c>
       <c r="F11">
-        <v>-0.7008337614468071</v>
+        <v>0.1369231858634309</v>
       </c>
       <c r="G11">
-        <v>-14.14230500296942</v>
+        <v>-13.59469610349423</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.489930330713646</v>
       </c>
       <c r="E12">
-        <v>-25.8058026602754</v>
+        <v>-25.08652875698497</v>
       </c>
       <c r="F12">
-        <v>-1.002470497297802</v>
+        <v>0.4544910836050662</v>
       </c>
       <c r="G12">
-        <v>-13.22113771367478</v>
+        <v>-13.01889116243501</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.343444816915408</v>
       </c>
       <c r="E13">
-        <v>-27.18184048320627</v>
+        <v>-25.45850282287059</v>
       </c>
       <c r="F13">
-        <v>-1.365168679511357</v>
+        <v>0.3446942978336029</v>
       </c>
       <c r="G13">
-        <v>-12.29479201248367</v>
+        <v>-13.18816009337213</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.383933029401443</v>
       </c>
       <c r="E14">
-        <v>-27.36427029064936</v>
+        <v>-26.02435709982185</v>
       </c>
       <c r="F14">
-        <v>-0.2135193006257055</v>
+        <v>0.5441428025078483</v>
       </c>
       <c r="G14">
-        <v>-12.58866786663775</v>
+        <v>-11.55578159480019</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.589873435799447</v>
       </c>
       <c r="E15">
-        <v>-27.65508230082518</v>
+        <v>-26.67753679808896</v>
       </c>
       <c r="F15">
-        <v>-0.736473440584853</v>
+        <v>0.6972284120148081</v>
       </c>
       <c r="G15">
-        <v>-11.57383358827544</v>
+        <v>-11.22586049544891</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.944809755687871</v>
       </c>
       <c r="E16">
-        <v>-28.81299346497605</v>
+        <v>-27.12613761291766</v>
       </c>
       <c r="F16">
-        <v>-0.7681800312944069</v>
+        <v>0.8528844455726549</v>
       </c>
       <c r="G16">
-        <v>-11.18233416162587</v>
+        <v>-11.14371341688953</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.416424440427919</v>
       </c>
       <c r="E17">
-        <v>-29.74796024521013</v>
+        <v>-27.21769515657351</v>
       </c>
       <c r="F17">
-        <v>-0.3040482606080523</v>
+        <v>0.922179035551639</v>
       </c>
       <c r="G17">
-        <v>-10.02433056600379</v>
+        <v>-10.67160202950015</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.973034423942882</v>
       </c>
       <c r="E18">
-        <v>-29.84972430569674</v>
+        <v>-29.16650235331148</v>
       </c>
       <c r="F18">
-        <v>-0.1256858481720683</v>
+        <v>0.9801912615044941</v>
       </c>
       <c r="G18">
-        <v>-10.59991750988965</v>
+        <v>-10.25862531247178</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.588460299664499</v>
       </c>
       <c r="E19">
-        <v>-31.51634778878622</v>
+        <v>-29.045631444125</v>
       </c>
       <c r="F19">
-        <v>0.2399083064816739</v>
+        <v>1.300668385564761</v>
       </c>
       <c r="G19">
-        <v>-9.589186016652283</v>
+        <v>-10.09010174911542</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.235640799631714</v>
       </c>
       <c r="E20">
-        <v>-29.75102116195653</v>
+        <v>-29.68701602222959</v>
       </c>
       <c r="F20">
-        <v>0.4539692121413025</v>
+        <v>1.009298435304063</v>
       </c>
       <c r="G20">
-        <v>-9.586559607593623</v>
+        <v>-9.88943078223638</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.9031958051665471</v>
       </c>
       <c r="E21">
-        <v>-31.23167837815982</v>
+        <v>-30.32459002894366</v>
       </c>
       <c r="F21">
-        <v>0.1137686602203792</v>
+        <v>1.321233434706662</v>
       </c>
       <c r="G21">
-        <v>-9.354141986486649</v>
+        <v>-9.391610087486011</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5787352891535839</v>
       </c>
       <c r="E22">
-        <v>-30.6560536715669</v>
+        <v>-31.56768978718375</v>
       </c>
       <c r="F22">
-        <v>0.65059546907421</v>
+        <v>1.511898759809024</v>
       </c>
       <c r="G22">
-        <v>-8.227056133684837</v>
+        <v>-9.036803370692239</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2679622001738889</v>
       </c>
       <c r="E23">
-        <v>-32.04034600200586</v>
+        <v>-31.40670300981075</v>
       </c>
       <c r="F23">
-        <v>0.8430384706229799</v>
+        <v>1.431008682925652</v>
       </c>
       <c r="G23">
-        <v>-9.20812695762257</v>
+        <v>-9.186060944338481</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.02530637176966064</v>
       </c>
       <c r="E24">
-        <v>-32.51517642295652</v>
+        <v>-31.70631982799521</v>
       </c>
       <c r="F24">
-        <v>1.025062266979338</v>
+        <v>1.827770161109726</v>
       </c>
       <c r="G24">
-        <v>-8.803030773142476</v>
+        <v>-9.026569251895074</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.2834922698596465</v>
       </c>
       <c r="E25">
-        <v>-34.63253754810134</v>
+        <v>-31.24769523763403</v>
       </c>
       <c r="F25">
-        <v>0.3579166983170886</v>
+        <v>1.551365496348003</v>
       </c>
       <c r="G25">
-        <v>-9.572706996793176</v>
+        <v>-9.003568592047365</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.4929880522209705</v>
       </c>
       <c r="E26">
-        <v>-32.77469813901109</v>
+        <v>-31.3352677750237</v>
       </c>
       <c r="F26">
-        <v>0.1592203512445852</v>
+        <v>1.564655822958519</v>
       </c>
       <c r="G26">
-        <v>-9.152369285390163</v>
+        <v>-8.794839561987859</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.637639168160516</v>
       </c>
       <c r="E27">
-        <v>-33.12690084238486</v>
+        <v>-31.5361233045094</v>
       </c>
       <c r="F27">
-        <v>0.5604525283015678</v>
+        <v>2.164246373187662</v>
       </c>
       <c r="G27">
-        <v>-9.182005152616187</v>
+        <v>-9.26688568076246</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.7090091549165347</v>
       </c>
       <c r="E28">
-        <v>-33.36919296125837</v>
+        <v>-31.26112049324153</v>
       </c>
       <c r="F28">
-        <v>0.4165907898247804</v>
+        <v>1.703750307032195</v>
       </c>
       <c r="G28">
-        <v>-9.585810323895974</v>
+        <v>-9.373311378646898</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.704691163123451</v>
       </c>
       <c r="E29">
-        <v>-33.34501088831956</v>
+        <v>-31.50908589878476</v>
       </c>
       <c r="F29">
-        <v>0.05412537885141194</v>
+        <v>1.666540043298441</v>
       </c>
       <c r="G29">
-        <v>-9.60798859919748</v>
+        <v>-9.775590569713181</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.6310713264185656</v>
       </c>
       <c r="E30">
-        <v>-32.19240129842483</v>
+        <v>-31.2677635547556</v>
       </c>
       <c r="F30">
-        <v>0.9135888655846082</v>
+        <v>1.674991047541802</v>
       </c>
       <c r="G30">
-        <v>-9.734992185949073</v>
+        <v>-9.337127763986365</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.5015948975568212</v>
       </c>
       <c r="E31">
-        <v>-32.9916141366899</v>
+        <v>-31.35879987039018</v>
       </c>
       <c r="F31">
-        <v>0.4208013813332103</v>
+        <v>1.762022640349529</v>
       </c>
       <c r="G31">
-        <v>-9.910710961398543</v>
+        <v>-9.964228614771775</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.3338261014069291</v>
       </c>
       <c r="E32">
-        <v>-32.29731349309566</v>
+        <v>-31.47608655820333</v>
       </c>
       <c r="F32">
-        <v>0.6908491546458492</v>
+        <v>1.914384256746442</v>
       </c>
       <c r="G32">
-        <v>-10.69433508802727</v>
+        <v>-10.29693929471866</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1460432737127054</v>
       </c>
       <c r="E33">
-        <v>-33.11039598057999</v>
+        <v>-30.81060504799208</v>
       </c>
       <c r="F33">
-        <v>0.1548697656450822</v>
+        <v>1.93524751815335</v>
       </c>
       <c r="G33">
-        <v>-9.645174739781002</v>
+        <v>-10.01959467531552</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.04614528905251143</v>
       </c>
       <c r="E34">
-        <v>-31.29909330438444</v>
+        <v>-30.59801461990808</v>
       </c>
       <c r="F34">
-        <v>0.5033722156768622</v>
+        <v>1.868969842255362</v>
       </c>
       <c r="G34">
-        <v>-10.39446496429199</v>
+        <v>-9.557641695130156</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2298879489138143</v>
       </c>
       <c r="E35">
-        <v>-31.69368368253942</v>
+        <v>-29.74863929526174</v>
       </c>
       <c r="F35">
-        <v>0.961231588389219</v>
+        <v>2.034368304837534</v>
       </c>
       <c r="G35">
-        <v>-10.11100206493957</v>
+        <v>-9.870946710531298</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.3974491393346707</v>
       </c>
       <c r="E36">
-        <v>-30.03333362515608</v>
+        <v>-29.37984035943395</v>
       </c>
       <c r="F36">
-        <v>0.6041522222688529</v>
+        <v>2.07926084786485</v>
       </c>
       <c r="G36">
-        <v>-9.47755318868087</v>
+        <v>-10.07945382730056</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5445982373837388</v>
       </c>
       <c r="E37">
-        <v>-31.0073322854209</v>
+        <v>-29.04881280399982</v>
       </c>
       <c r="F37">
-        <v>0.6422438689191854</v>
+        <v>2.251059277001051</v>
       </c>
       <c r="G37">
-        <v>-10.92596165352313</v>
+        <v>-9.982469887229884</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6741165677156387</v>
       </c>
       <c r="E38">
-        <v>-29.89031779318561</v>
+        <v>-29.14385073874587</v>
       </c>
       <c r="F38">
-        <v>0.5886269604055846</v>
+        <v>1.857738837008206</v>
       </c>
       <c r="G38">
-        <v>-10.31031675000353</v>
+        <v>-10.43452814541492</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7899743595027826</v>
       </c>
       <c r="E39">
-        <v>-28.30588636221449</v>
+        <v>-27.95309182622692</v>
       </c>
       <c r="F39">
-        <v>0.2994571539667219</v>
+        <v>2.097786456461058</v>
       </c>
       <c r="G39">
-        <v>-10.36957412536032</v>
+        <v>-10.35612226385461</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9021637181096596</v>
       </c>
       <c r="E40">
-        <v>-28.04934665189115</v>
+        <v>-28.80400799227478</v>
       </c>
       <c r="F40">
-        <v>0.9979415182116819</v>
+        <v>1.835076361602417</v>
       </c>
       <c r="G40">
-        <v>-11.0090812344427</v>
+        <v>-10.56868386697387</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.018442957159888</v>
       </c>
       <c r="E41">
-        <v>-29.69572738298342</v>
+        <v>-26.71833794614408</v>
       </c>
       <c r="F41">
-        <v>0.9488590928610056</v>
+        <v>1.951389085364302</v>
       </c>
       <c r="G41">
-        <v>-10.53035813637633</v>
+        <v>-10.25463217861967</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.149751159156738</v>
       </c>
       <c r="E42">
-        <v>-28.34111805388301</v>
+        <v>-26.80533526376526</v>
       </c>
       <c r="F42">
-        <v>1.103139208162802</v>
+        <v>2.203603765229473</v>
       </c>
       <c r="G42">
-        <v>-9.767670875996037</v>
+        <v>-10.16270655619428</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.302604463708869</v>
       </c>
       <c r="E43">
-        <v>-28.61163539692005</v>
+        <v>-26.80215805710176</v>
       </c>
       <c r="F43">
-        <v>0.5403902981731665</v>
+        <v>2.075844660695705</v>
       </c>
       <c r="G43">
-        <v>-10.32312767371212</v>
+        <v>-10.45362835284351</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.482515440279655</v>
       </c>
       <c r="E44">
-        <v>-28.04794701967468</v>
+        <v>-25.96629520550075</v>
       </c>
       <c r="F44">
-        <v>1.190886510406548</v>
+        <v>2.091794046669206</v>
       </c>
       <c r="G44">
-        <v>-10.95027812864476</v>
+        <v>-10.16157088229714</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.690488624708152</v>
       </c>
       <c r="E45">
-        <v>-27.80643362792458</v>
+        <v>-25.09348123274273</v>
       </c>
       <c r="F45">
-        <v>1.048461989373618</v>
+        <v>2.160989232559855</v>
       </c>
       <c r="G45">
-        <v>-10.75856332108554</v>
+        <v>-10.51615829654526</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.923470029376927</v>
       </c>
       <c r="E46">
-        <v>-27.35290710446463</v>
+        <v>-25.05765978506608</v>
       </c>
       <c r="F46">
-        <v>0.9745633333698742</v>
+        <v>1.810392669733798</v>
       </c>
       <c r="G46">
-        <v>-11.46301139649957</v>
+        <v>-10.55958803281843</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.177402299635772</v>
       </c>
       <c r="E47">
-        <v>-25.93100536887368</v>
+        <v>-25.10810468981745</v>
       </c>
       <c r="F47">
-        <v>1.159262756437274</v>
+        <v>2.255017216451627</v>
       </c>
       <c r="G47">
-        <v>-11.2356455661764</v>
+        <v>-10.75162657270695</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.441999320233025</v>
       </c>
       <c r="E48">
-        <v>-24.91710265419991</v>
+        <v>-24.49923560317494</v>
       </c>
       <c r="F48">
-        <v>0.6001122744453997</v>
+        <v>2.367391881580602</v>
       </c>
       <c r="G48">
-        <v>-11.05447686139298</v>
+        <v>-10.65924929146729</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.712509886497009</v>
       </c>
       <c r="E49">
-        <v>-25.16558513455308</v>
+        <v>-24.65159200741495</v>
       </c>
       <c r="F49">
-        <v>0.8410868370219843</v>
+        <v>2.518978146088495</v>
       </c>
       <c r="G49">
-        <v>-10.74345233139218</v>
+        <v>-10.92095946688656</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.97809414689969</v>
       </c>
       <c r="E50">
-        <v>-25.56641986593493</v>
+        <v>-24.10955639741157</v>
       </c>
       <c r="F50">
-        <v>0.9727608059013825</v>
+        <v>2.331511975895745</v>
       </c>
       <c r="G50">
-        <v>-11.22191043888255</v>
+        <v>-11.17924695614687</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.237183659164369</v>
       </c>
       <c r="E51">
-        <v>-25.53049043476384</v>
+        <v>-23.37459996815859</v>
       </c>
       <c r="F51">
-        <v>0.6373473892012375</v>
+        <v>1.832877874515388</v>
       </c>
       <c r="G51">
-        <v>-12.03430758164993</v>
+        <v>-11.40377882321639</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.48381652442409</v>
       </c>
       <c r="E52">
-        <v>-24.92784285868592</v>
+        <v>-23.96269469175431</v>
       </c>
       <c r="F52">
-        <v>0.4950015630715732</v>
+        <v>2.006995732379427</v>
       </c>
       <c r="G52">
-        <v>-11.40031175439939</v>
+        <v>-10.97925217211694</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.720449089290639</v>
       </c>
       <c r="E53">
-        <v>-24.88616953625259</v>
+        <v>-21.98062027230446</v>
       </c>
       <c r="F53">
-        <v>1.100501686352289</v>
+        <v>2.353650923102964</v>
       </c>
       <c r="G53">
-        <v>-11.35373346014934</v>
+        <v>-11.18144911920948</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.947601670515129</v>
       </c>
       <c r="E54">
-        <v>-22.68430302028149</v>
+        <v>-22.24888449819779</v>
       </c>
       <c r="F54">
-        <v>1.164383723721381</v>
+        <v>1.916693745065447</v>
       </c>
       <c r="G54">
-        <v>-11.42253832847583</v>
+        <v>-11.2907296663043</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.170056176706562</v>
       </c>
       <c r="E55">
-        <v>-24.91355581172851</v>
+        <v>-21.92365897898444</v>
       </c>
       <c r="F55">
-        <v>0.9978255467752899</v>
+        <v>1.776422979279796</v>
       </c>
       <c r="G55">
-        <v>-11.38067634432963</v>
+        <v>-10.93147685147186</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.393457281827384</v>
       </c>
       <c r="E56">
-        <v>-23.44534576986572</v>
+        <v>-21.49535075468885</v>
       </c>
       <c r="F56">
-        <v>0.8813637168809019</v>
+        <v>2.057259409646495</v>
       </c>
       <c r="G56">
-        <v>-11.77589869276613</v>
+        <v>-11.76129027140656</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.621434042145941</v>
       </c>
       <c r="E57">
-        <v>-24.22153943436293</v>
+        <v>-20.6862802693443</v>
       </c>
       <c r="F57">
-        <v>1.019820358054423</v>
+        <v>2.33309084416548</v>
       </c>
       <c r="G57">
-        <v>-12.19006068783886</v>
+        <v>-11.90266470175993</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.86257313003711</v>
       </c>
       <c r="E58">
-        <v>-22.79143510640544</v>
+        <v>-20.9284124895818</v>
       </c>
       <c r="F58">
-        <v>0.1940954472698472</v>
+        <v>2.215684675431901</v>
       </c>
       <c r="G58">
-        <v>-12.05391557890149</v>
+        <v>-12.21913132886091</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.115687782310061</v>
       </c>
       <c r="E59">
-        <v>-22.56116445771165</v>
+        <v>-20.65501904770231</v>
       </c>
       <c r="F59">
-        <v>0.6092731895529594</v>
+        <v>2.116774294068029</v>
       </c>
       <c r="G59">
-        <v>-12.03362748268395</v>
+        <v>-12.28135059395632</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.388266409986755</v>
       </c>
       <c r="E60">
-        <v>-22.61681333625302</v>
+        <v>-20.66059681051156</v>
       </c>
       <c r="F60">
-        <v>0.3964142449947929</v>
+        <v>2.137299581574595</v>
       </c>
       <c r="G60">
-        <v>-12.27073008495967</v>
+        <v>-11.9967716012912</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.67256404933836</v>
       </c>
       <c r="E61">
-        <v>-20.89557720084771</v>
+        <v>-19.89873172508501</v>
       </c>
       <c r="F61">
-        <v>0.6775074692563603</v>
+        <v>1.824577633139336</v>
       </c>
       <c r="G61">
-        <v>-12.47065307351336</v>
+        <v>-12.19382668691155</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.971394236678054</v>
       </c>
       <c r="E62">
-        <v>-20.42885177179745</v>
+        <v>-19.06837187848939</v>
       </c>
       <c r="F62">
-        <v>1.02816698800503</v>
+        <v>1.816905294254608</v>
       </c>
       <c r="G62">
-        <v>-11.79554324044196</v>
+        <v>-12.84414097322884</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.274789085964358</v>
       </c>
       <c r="E63">
-        <v>-22.6283011187775</v>
+        <v>-19.46058869637222</v>
       </c>
       <c r="F63">
-        <v>0.02226636853974296</v>
+        <v>2.047317344078095</v>
       </c>
       <c r="G63">
-        <v>-12.33275093346616</v>
+        <v>-13.04498555462319</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.581469055299978</v>
       </c>
       <c r="E64">
-        <v>-20.71097526388173</v>
+        <v>-18.85864716621952</v>
       </c>
       <c r="F64">
-        <v>0.3740375563429698</v>
+        <v>1.999272034715724</v>
       </c>
       <c r="G64">
-        <v>-12.6277833474741</v>
+        <v>-12.75240201904171</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.884334889630884</v>
       </c>
       <c r="E65">
-        <v>-21.92071019894381</v>
+        <v>-19.47641658473115</v>
       </c>
       <c r="F65">
-        <v>0.9436039300576455</v>
+        <v>1.68754247042902</v>
       </c>
       <c r="G65">
-        <v>-12.97995190685855</v>
+        <v>-13.04966139818587</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.179350094669966</v>
       </c>
       <c r="E66">
-        <v>-20.71389081823176</v>
+        <v>-18.54256701834345</v>
       </c>
       <c r="F66">
-        <v>0.6089426709592424</v>
+        <v>1.948698548040009</v>
       </c>
       <c r="G66">
-        <v>-13.1357585333116</v>
+        <v>-13.04651545095358</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.464316815920376</v>
       </c>
       <c r="E67">
-        <v>-20.12385239173602</v>
+        <v>-20.01846465436849</v>
       </c>
       <c r="F67">
-        <v>0.5840667978531733</v>
+        <v>1.944844982882185</v>
       </c>
       <c r="G67">
-        <v>-12.27426242239145</v>
+        <v>-12.88801192533791</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.733159239631477</v>
       </c>
       <c r="E68">
-        <v>-21.15510722332492</v>
+        <v>-18.73649291473367</v>
       </c>
       <c r="F68">
-        <v>0.6365322756768828</v>
+        <v>1.867752142173247</v>
       </c>
       <c r="G68">
-        <v>-12.22178645611007</v>
+        <v>-12.98239034230665</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.990369260385304</v>
       </c>
       <c r="E69">
-        <v>-19.25495905046864</v>
+        <v>-19.48858549391289</v>
       </c>
       <c r="F69">
-        <v>0.3916884089618217</v>
+        <v>1.619709120548574</v>
       </c>
       <c r="G69">
-        <v>-12.82003596841909</v>
+        <v>-12.98571382017114</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.229240525409626</v>
       </c>
       <c r="E70">
-        <v>-21.86516930389688</v>
+        <v>-19.13746470208924</v>
       </c>
       <c r="F70">
-        <v>0.251674437071038</v>
+        <v>1.566682009625766</v>
       </c>
       <c r="G70">
-        <v>-12.94676020549944</v>
+        <v>-12.87886387629065</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.460177147910379</v>
       </c>
       <c r="E71">
-        <v>-20.74199144605555</v>
+        <v>-19.12909182805839</v>
       </c>
       <c r="F71">
-        <v>0.2310919922136787</v>
+        <v>1.583318940543592</v>
       </c>
       <c r="G71">
-        <v>-12.91352803759915</v>
+        <v>-12.82007382421566</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.676401802565737</v>
       </c>
       <c r="E72">
-        <v>-21.32373175632428</v>
+        <v>-19.40064124410965</v>
       </c>
       <c r="F72">
-        <v>-0.2461660883374368</v>
+        <v>1.793588408600607</v>
       </c>
       <c r="G72">
-        <v>-12.59152793733731</v>
+        <v>-13.24754147909701</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.889644109894423</v>
       </c>
       <c r="E73">
-        <v>-19.45574189875615</v>
+        <v>-18.93400718570854</v>
       </c>
       <c r="F73">
-        <v>-0.2486064587060842</v>
+        <v>1.64596008354329</v>
       </c>
       <c r="G73">
-        <v>-13.02027746781289</v>
+        <v>-13.05072005511757</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.095511191603556</v>
       </c>
       <c r="E74">
-        <v>-21.1737219164828</v>
+        <v>-19.70011269989774</v>
       </c>
       <c r="F74">
-        <v>-0.3577306101464742</v>
+        <v>1.56205806278334</v>
       </c>
       <c r="G74">
-        <v>-13.59512296023487</v>
+        <v>-13.01267759030816</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.300283408632296</v>
       </c>
       <c r="E75">
-        <v>-20.67451006844973</v>
+        <v>-19.38618391548792</v>
       </c>
       <c r="F75">
-        <v>-0.01689884226461767</v>
+        <v>1.591937275002318</v>
       </c>
       <c r="G75">
-        <v>-11.83086139327054</v>
+        <v>-12.24464483037757</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.501929878780039</v>
       </c>
       <c r="E76">
-        <v>-22.89137798372612</v>
+        <v>-20.40307694231556</v>
       </c>
       <c r="F76">
-        <v>0.7112162239784806</v>
+        <v>1.719794126889616</v>
       </c>
       <c r="G76">
-        <v>-11.66374763199338</v>
+        <v>-12.37312870931232</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.696929807353929</v>
       </c>
       <c r="E77">
-        <v>-20.85366299215754</v>
+        <v>-20.92604931233798</v>
       </c>
       <c r="F77">
-        <v>0.3232312984270677</v>
+        <v>1.272908137162144</v>
       </c>
       <c r="G77">
-        <v>-11.35423341773854</v>
+        <v>-12.46553862485936</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.88373100933828</v>
       </c>
       <c r="E78">
-        <v>-22.02106009097432</v>
+        <v>-20.59119664927367</v>
       </c>
       <c r="F78">
-        <v>-0.3944529654799792</v>
+        <v>1.518456116169585</v>
       </c>
       <c r="G78">
-        <v>-12.47604948258319</v>
+        <v>-12.47609386524124</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.0510910324241</v>
       </c>
       <c r="E79">
-        <v>-23.1382240988173</v>
+        <v>-21.67555444086183</v>
       </c>
       <c r="F79">
-        <v>-0.6595876917266141</v>
+        <v>1.445693980242482</v>
       </c>
       <c r="G79">
-        <v>-11.58917693423741</v>
+        <v>-12.08315069683278</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.19788460962633</v>
       </c>
       <c r="E80">
-        <v>-23.4229267351343</v>
+        <v>-20.81009580536009</v>
       </c>
       <c r="F80">
-        <v>0.5519534787488448</v>
+        <v>1.314389463224732</v>
       </c>
       <c r="G80">
-        <v>-11.68141715138604</v>
+        <v>-12.16151089036275</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.30547071266114</v>
       </c>
       <c r="E81">
-        <v>-22.27014478696958</v>
+        <v>-21.93886388564464</v>
       </c>
       <c r="F81">
-        <v>-0.3355775806934071</v>
+        <v>1.398602950128136</v>
       </c>
       <c r="G81">
-        <v>-11.15159003332091</v>
+        <v>-11.87257325960276</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.37065704651067</v>
       </c>
       <c r="E82">
-        <v>-24.5206080286525</v>
+        <v>-22.74295051739939</v>
       </c>
       <c r="F82">
-        <v>-0.1625796755579527</v>
+        <v>1.288290919832131</v>
       </c>
       <c r="G82">
-        <v>-11.62727030856635</v>
+        <v>-11.48758894608031</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.37290815051519</v>
       </c>
       <c r="E83">
-        <v>-24.12207832955593</v>
+        <v>-23.16213828962566</v>
       </c>
       <c r="F83">
-        <v>-0.06108478789734609</v>
+        <v>1.273161617587401</v>
       </c>
       <c r="G83">
-        <v>-11.62361396076649</v>
+        <v>-11.31475112728713</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.30787544986979</v>
       </c>
       <c r="E84">
-        <v>-26.5184148126008</v>
+        <v>-24.31700930308676</v>
       </c>
       <c r="F84">
-        <v>-0.5701140718154339</v>
+        <v>1.512743694559879</v>
       </c>
       <c r="G84">
-        <v>-11.65690487042007</v>
+        <v>-11.82476138853341</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.16092033105281</v>
       </c>
       <c r="E85">
-        <v>-26.59880021779286</v>
+        <v>-24.35767339516816</v>
       </c>
       <c r="F85">
-        <v>-0.0563896014582785</v>
+        <v>1.334454178455342</v>
       </c>
       <c r="G85">
-        <v>-10.87016351474956</v>
+        <v>-11.67490987049269</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.926880912450796</v>
       </c>
       <c r="E86">
-        <v>-26.72703061744694</v>
+        <v>-26.26232780231188</v>
       </c>
       <c r="F86">
-        <v>-0.317299653950636</v>
+        <v>1.304738982982118</v>
       </c>
       <c r="G86">
-        <v>-9.750231102127401</v>
+        <v>-11.45356702794122</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.603404322695926</v>
       </c>
       <c r="E87">
-        <v>-26.75028444765466</v>
+        <v>-26.86605106012293</v>
       </c>
       <c r="F87">
-        <v>-0.3062177548359842</v>
+        <v>1.215601680236474</v>
       </c>
       <c r="G87">
-        <v>-10.78711964542314</v>
+        <v>-11.46170210808712</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.19102208243007</v>
       </c>
       <c r="E88">
-        <v>-27.71895038457839</v>
+        <v>-27.17750037737182</v>
       </c>
       <c r="F88">
-        <v>0.01344591243473382</v>
+        <v>1.076719258217915</v>
       </c>
       <c r="G88">
-        <v>-10.48716206174406</v>
+        <v>-10.78195689799421</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.702697030950157</v>
       </c>
       <c r="E89">
-        <v>-29.16116132354775</v>
+        <v>-29.28573689723599</v>
       </c>
       <c r="F89">
-        <v>-0.5257939306634519</v>
+        <v>1.315759582908963</v>
       </c>
       <c r="G89">
-        <v>-9.963581150113178</v>
+        <v>-10.67619693998051</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.145904068398766</v>
       </c>
       <c r="E90">
-        <v>-31.65926809689622</v>
+        <v>-29.65779195074244</v>
       </c>
       <c r="F90">
-        <v>-1.304498222562919</v>
+        <v>1.010411761093426</v>
       </c>
       <c r="G90">
-        <v>-10.67089973920514</v>
+        <v>-10.7715883258506</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.545511742016929</v>
       </c>
       <c r="E91">
-        <v>-31.90542477890748</v>
+        <v>-31.44743355327334</v>
       </c>
       <c r="F91">
-        <v>-0.5405852590078399</v>
+        <v>1.317361645465977</v>
       </c>
       <c r="G91">
-        <v>-11.40008723036456</v>
+        <v>-10.2847666980626</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.913119253635742</v>
       </c>
       <c r="E92">
-        <v>-34.11171238833386</v>
+        <v>-32.59176163978636</v>
       </c>
       <c r="F92">
-        <v>-1.032259417469875</v>
+        <v>1.190855032445242</v>
       </c>
       <c r="G92">
-        <v>-10.67554033771584</v>
+        <v>-10.39264919142887</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.274801466139083</v>
       </c>
       <c r="E93">
-        <v>-35.02083165788787</v>
+        <v>-33.9331762165078</v>
       </c>
       <c r="F93">
-        <v>-0.9173549182927503</v>
+        <v>0.9152820485559304</v>
       </c>
       <c r="G93">
-        <v>-10.32643026561988</v>
+        <v>-10.20435968077319</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.641213165988134</v>
       </c>
       <c r="E94">
-        <v>-35.16664260107995</v>
+        <v>-36.03385389176078</v>
       </c>
       <c r="F94">
-        <v>-0.4906653542129333</v>
+        <v>0.8615110637054089</v>
       </c>
       <c r="G94">
-        <v>-10.82048757204215</v>
+        <v>-9.570867727228736</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.027589972297293</v>
       </c>
       <c r="E95">
-        <v>-39.59474252386492</v>
+        <v>-37.79018050964957</v>
       </c>
       <c r="F95">
-        <v>-0.4387101507093483</v>
+        <v>0.8606147701755799</v>
       </c>
       <c r="G95">
-        <v>-10.88858753932905</v>
+        <v>-9.997322413208726</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.436039604617275</v>
       </c>
       <c r="E96">
-        <v>-40.01648867426729</v>
+        <v>-39.3159083751499</v>
       </c>
       <c r="F96">
-        <v>-1.12178770962964</v>
+        <v>0.646422154098906</v>
       </c>
       <c r="G96">
-        <v>-10.93551567335431</v>
+        <v>-9.70599986726476</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.869308139295094</v>
       </c>
       <c r="E97">
-        <v>-41.04465559323617</v>
+        <v>-40.91041757340073</v>
       </c>
       <c r="F97">
-        <v>-1.505259689570601</v>
+        <v>0.3945595303799247</v>
       </c>
       <c r="G97">
-        <v>-10.46789737740624</v>
+        <v>-9.879832379747151</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.320017595332496</v>
       </c>
       <c r="E98">
-        <v>-42.99914022985519</v>
+        <v>-42.68027743039148</v>
       </c>
       <c r="F98">
-        <v>-1.092831298697381</v>
+        <v>0.4135465396194922</v>
       </c>
       <c r="G98">
-        <v>-11.00136517880367</v>
+        <v>-9.592529075101202</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.789747786738854</v>
       </c>
       <c r="E99">
-        <v>-44.75470473346587</v>
+        <v>-44.20278032729809</v>
       </c>
       <c r="F99">
-        <v>-1.94171156349241</v>
+        <v>-0.07475450677834354</v>
       </c>
       <c r="G99">
-        <v>-10.97476038604793</v>
+        <v>-9.604294395601055</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.265044287344434</v>
       </c>
       <c r="E100">
-        <v>-46.95195703165509</v>
+        <v>-46.38606745240757</v>
       </c>
       <c r="F100">
-        <v>-2.008026515923525</v>
+        <v>-0.02868236856944063</v>
       </c>
       <c r="G100">
-        <v>-11.71855107707774</v>
+        <v>-10.40251780598328</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.764825817578378</v>
       </c>
       <c r="E101">
-        <v>-49.42981586149219</v>
+        <v>-47.65689093454372</v>
       </c>
       <c r="F101">
-        <v>-2.032403711853109</v>
+        <v>-0.4940542052577861</v>
       </c>
       <c r="G101">
-        <v>-11.37768051491133</v>
+        <v>-10.13516189538574</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.258491830033778</v>
       </c>
       <c r="E102">
-        <v>-50.47510543245052</v>
+        <v>-49.91529719288537</v>
       </c>
       <c r="F102">
-        <v>-2.079527876663567</v>
+        <v>-0.8574937762968468</v>
       </c>
       <c r="G102">
-        <v>-10.78637819395926</v>
+        <v>-9.741456389556669</v>
       </c>
     </row>
   </sheetData>
